--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9614,0.0003,0.0045,0.0087</t>
-  </si>
-  <si>
-    <t>0.8023,0.0003,0.0032,0.1534</t>
-  </si>
-  <si>
-    <t>0.9358,0.0010,0.0019,0.0663</t>
-  </si>
-  <si>
-    <t>0.9670,0.0003,0.0004,0.0257</t>
-  </si>
-  <si>
-    <t>0.9837,0.0015,0.0006,0.0080</t>
-  </si>
-  <si>
-    <t>0.9406,0.0012,0.0007,0.0620</t>
-  </si>
-  <si>
-    <t>0.9502,0.0003,0.0003,0.0647</t>
-  </si>
-  <si>
-    <t>0.9643,0.0024,0.0005,0.0119</t>
-  </si>
-  <si>
-    <t>0.9074,0.0042,0.0031,0.0750</t>
-  </si>
-  <si>
-    <t>0.8987,0.0015,0.0012,0.1286</t>
-  </si>
-  <si>
-    <t>0.8372,0.0044,0.0042,0.1626</t>
-  </si>
-  <si>
-    <t>0.9614,0.0010,0.0005,0.0325</t>
-  </si>
-  <si>
-    <t>0.9479,0.0015,0.0591,0.0010</t>
-  </si>
-  <si>
-    <t>0.1467,0.0128,0.8796,0.0030</t>
-  </si>
-  <si>
-    <t>0.8804,0.0037,0.1786,0.0010</t>
-  </si>
-  <si>
-    <t>0.9684,0.0016,0.0305,0.0002</t>
-  </si>
-  <si>
-    <t>0.9253,0.0055,0.0627,0.0037</t>
-  </si>
-  <si>
-    <t>0.9146,0.0278,0.0179,0.0008</t>
-  </si>
-  <si>
-    <t>0.9826,0.0047,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9653,0.0072,0.0074,0.0022</t>
-  </si>
-  <si>
-    <t>0.8269,0.0513,0.1103,0.0071</t>
-  </si>
-  <si>
-    <t>0.9266,0.0361,0.0131,0.0009</t>
-  </si>
-  <si>
-    <t>0.9667,0.0010,0.0290,0.0005</t>
-  </si>
-  <si>
-    <t>0.9244,0.0079,0.0570,0.0024</t>
-  </si>
-  <si>
-    <t>0.6894,0.0080,0.4788,0.0039</t>
-  </si>
-  <si>
-    <t>0.7354,0.0021,0.2885,0.0033</t>
-  </si>
-  <si>
-    <t>0.9747,0.0013,0.0124,0.0018</t>
-  </si>
-  <si>
-    <t>0.9589,0.0005,0.0721,0.0002</t>
-  </si>
-  <si>
-    <t>0.0081,0.0077,0.9927,0.0012</t>
-  </si>
-  <si>
-    <t>0.9748,0.0042,0.0101,0.0005</t>
-  </si>
-  <si>
-    <t>0.9784,0.0012,0.0032,0.0034</t>
-  </si>
-  <si>
-    <t>0.0239,0.0213,0.9779,0.0027</t>
-  </si>
-  <si>
-    <t>0.9014,0.0281,0.0542,0.0008</t>
-  </si>
-  <si>
-    <t>0.9586,0.0057,0.0079,0.0024</t>
-  </si>
-  <si>
-    <t>0.8172,0.0141,0.1188,0.0276</t>
-  </si>
-  <si>
-    <t>0.9738,0.0049,0.0041,0.0027</t>
-  </si>
-  <si>
-    <t>0.9869,0.0014,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.1019,0.6814,0.5640,0.0089</t>
-  </si>
-  <si>
-    <t>0.4843,0.0034,0.7486,0.0004</t>
-  </si>
-  <si>
-    <t>0.1515,0.0062,0.9340,0.0004</t>
-  </si>
-  <si>
-    <t>0.9845,0.0003,0.0109,0.0003</t>
-  </si>
-  <si>
-    <t>0.9420,0.0072,0.0643,0.0002</t>
-  </si>
-  <si>
-    <t>0.4396,0.1199,0.3838,0.0005</t>
-  </si>
-  <si>
-    <t>0.8171,0.0048,0.3762,0.0004</t>
-  </si>
-  <si>
-    <t>0.8793,0.0114,0.0691,0.0092</t>
-  </si>
-  <si>
-    <t>0.9458,0.0096,0.0221,0.0012</t>
-  </si>
-  <si>
-    <t>0.9622,0.0123,0.0089,0.0005</t>
-  </si>
-  <si>
-    <t>0.9880,0.0025,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.1693,0.0912,0.8639,0.0028</t>
-  </si>
-  <si>
-    <t>0.0717,0.0328,0.9586,0.0002</t>
-  </si>
-  <si>
-    <t>0.9552,0.0020,0.0568,0.0006</t>
-  </si>
-  <si>
-    <t>0.1339,0.0042,0.9128,0.0034</t>
-  </si>
-  <si>
-    <t>0.0169,0.0653,0.9782,0.0004</t>
-  </si>
-  <si>
-    <t>0.4997,0.0075,0.7331,0.0010</t>
-  </si>
-  <si>
-    <t>0.9677,0.0024,0.0017,0.0111</t>
-  </si>
-  <si>
-    <t>0.9659,0.0009,0.0014,0.0267</t>
-  </si>
-  <si>
-    <t>0.8569,0.0032,0.0096,0.1214</t>
-  </si>
-  <si>
-    <t>0.0482,0.6776,0.8478,0.0111</t>
-  </si>
-  <si>
-    <t>0.9750,0.0009,0.0005,0.0187</t>
-  </si>
-  <si>
-    <t>0.8524,0.0244,0.0111,0.0381</t>
-  </si>
-  <si>
-    <t>0.9615,0.0070,0.0030,0.0051</t>
-  </si>
-  <si>
-    <t>0.1144,0.1543,0.8895,0.0004</t>
-  </si>
-  <si>
-    <t>0.4538,0.0213,0.6629,0.0014</t>
-  </si>
-  <si>
-    <t>0.0175,0.0582,0.9789,0.0005</t>
-  </si>
-  <si>
-    <t>0.0056,0.8796,0.8959,0.0002</t>
-  </si>
-  <si>
-    <t>0.0641,0.0381,0.9527,0.0002</t>
-  </si>
-  <si>
-    <t>0.4028,0.4833,0.1569,0.0024</t>
-  </si>
-  <si>
-    <t>0.0613,0.9798,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.9505,0.0010,0.0118,0.0054</t>
-  </si>
-  <si>
-    <t>0.9858,0.0010,0.0061,0.0004</t>
-  </si>
-  <si>
-    <t>0.7808,0.0130,0.3524,0.0023</t>
-  </si>
-  <si>
-    <t>0.0741,0.3875,0.9017,0.0013</t>
-  </si>
-  <si>
-    <t>0.7050,0.0335,0.3479,0.0005</t>
-  </si>
-  <si>
-    <t>0.0074,0.9664,0.7730,0.0007</t>
-  </si>
-  <si>
-    <t>0.0075,0.8652,0.9621,0.0022</t>
-  </si>
-  <si>
-    <t>0.6674,0.0001,0.0018,0.3856</t>
-  </si>
-  <si>
-    <t>0.8748,0.0001,0.0010,0.1006</t>
-  </si>
-  <si>
-    <t>0.5278,0.0004,0.0010,0.7287</t>
-  </si>
-  <si>
-    <t>0.8308,0.0004,0.0021,0.2393</t>
-  </si>
-  <si>
-    <t>0.9718,0.0006,0.0017,0.0145</t>
-  </si>
-  <si>
-    <t>0.8152,0.0008,0.0058,0.2144</t>
-  </si>
-  <si>
-    <t>0.0384,0.8786,0.7705,0.0023</t>
-  </si>
-  <si>
-    <t>0.0074,0.2256,0.9862,0.0002</t>
-  </si>
-  <si>
-    <t>0.2381,0.0786,0.7601,0.0004</t>
-  </si>
-  <si>
-    <t>0.4180,0.0680,0.6203,0.0012</t>
-  </si>
-  <si>
-    <t>0.1421,0.5742,0.5443,0.0004</t>
-  </si>
-  <si>
-    <t>0.1834,0.1860,0.8714,0.0021</t>
-  </si>
-  <si>
-    <t>0.9692,0.0021,0.0007,0.0149</t>
-  </si>
-  <si>
-    <t>0.9529,0.0067,0.0042,0.0153</t>
-  </si>
-  <si>
-    <t>0.9781,0.0021,0.0012,0.0040</t>
-  </si>
-  <si>
-    <t>0.8077,0.0050,0.0032,0.1921</t>
-  </si>
-  <si>
-    <t>0.8382,0.0017,0.0022,0.2143</t>
-  </si>
-  <si>
-    <t>0.7306,0.0022,0.0038,0.3537</t>
-  </si>
-  <si>
-    <t>0.9805,0.0003,0.0003,0.0164</t>
-  </si>
-  <si>
-    <t>0.9712,0.0066,0.0017,0.0040</t>
-  </si>
-  <si>
-    <t>0.9631,0.0004,0.0002,0.0414</t>
-  </si>
-  <si>
-    <t>0.8519,0.0015,0.0029,0.2118</t>
-  </si>
-  <si>
-    <t>0.9113,0.0009,0.0008,0.1547</t>
-  </si>
-  <si>
-    <t>0.8341,0.0017,0.0012,0.2017</t>
-  </si>
-  <si>
-    <t>0.8687,0.0012,0.0024,0.1601</t>
-  </si>
-  <si>
-    <t>0.9301,0.0019,0.0019,0.0424</t>
-  </si>
-  <si>
-    <t>0.8626,0.0075,0.0047,0.0853</t>
-  </si>
-  <si>
-    <t>0.9304,0.0038,0.0057,0.0440</t>
-  </si>
-  <si>
-    <t>0.0473,0.0266,0.9603,0.0065</t>
-  </si>
-  <si>
-    <t>0.5305,0.0612,0.4696,0.0016</t>
-  </si>
-  <si>
-    <t>0.9686,0.0016,0.0119,0.0025</t>
-  </si>
-  <si>
-    <t>0.9347,0.0008,0.0488,0.0029</t>
-  </si>
-  <si>
-    <t>0.9146,0.0314,0.0065,0.0020</t>
-  </si>
-  <si>
-    <t>0.8675,0.0378,0.0525,0.0047</t>
-  </si>
-  <si>
-    <t>0.9032,0.0337,0.0123,0.0037</t>
-  </si>
-  <si>
-    <t>0.9426,0.0129,0.0107,0.0036</t>
-  </si>
-  <si>
-    <t>0.8862,0.0572,0.0262,0.0024</t>
-  </si>
-  <si>
-    <t>0.5680,0.3627,0.0709,0.0040</t>
-  </si>
-  <si>
-    <t>0.9513,0.0051,0.0133,0.0038</t>
-  </si>
-  <si>
-    <t>0.9804,0.0005,0.0060,0.0012</t>
-  </si>
-  <si>
-    <t>0.9118,0.0005,0.0355,0.0074</t>
-  </si>
-  <si>
-    <t>0.9353,0.0035,0.0478,0.0023</t>
-  </si>
-  <si>
-    <t>0.9550,0.0028,0.0280,0.0036</t>
-  </si>
-  <si>
-    <t>0.8967,0.0006,0.0136,0.0316</t>
-  </si>
-  <si>
-    <t>0.8805,0.1344,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.9911,0.0019,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.8812,0.0135,0.0903,0.0023</t>
-  </si>
-  <si>
-    <t>0.5865,0.4025,0.0339,0.0003</t>
-  </si>
-  <si>
-    <t>0.9836,0.0036,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.8295,0.0194,0.0805,0.0200</t>
-  </si>
-  <si>
-    <t>0.8333,0.0549,0.0382,0.0141</t>
-  </si>
-  <si>
-    <t>0.9711,0.0019,0.0015,0.0152</t>
-  </si>
-  <si>
-    <t>0.9658,0.0048,0.0036,0.0094</t>
-  </si>
-  <si>
-    <t>0.9361,0.0015,0.0020,0.0565</t>
-  </si>
-  <si>
-    <t>0.9608,0.0026,0.0027,0.0159</t>
-  </si>
-  <si>
-    <t>0.9245,0.0028,0.0063,0.0583</t>
-  </si>
-  <si>
-    <t>0.9871,0.0012,0.0027,0.0025</t>
-  </si>
-  <si>
-    <t>0.9430,0.0013,0.0030,0.0400</t>
-  </si>
-  <si>
-    <t>0.9524,0.0011,0.0013,0.0378</t>
-  </si>
-  <si>
-    <t>0.2880,0.1438,0.7531,0.0019</t>
-  </si>
-  <si>
-    <t>0.3232,0.1739,0.6691,0.0007</t>
-  </si>
-  <si>
-    <t>0.3909,0.0109,0.8090,0.0003</t>
-  </si>
-  <si>
-    <t>0.3829,0.0665,0.7184,0.0001</t>
-  </si>
-  <si>
-    <t>0.9872,0.0012,0.0055,0.0001</t>
-  </si>
-  <si>
-    <t>0.9837,0.0010,0.0082,0.0006</t>
-  </si>
-  <si>
-    <t>0.9430,0.0007,0.0177,0.0051</t>
-  </si>
-  <si>
-    <t>0.9851,0.0007,0.0064,0.0005</t>
-  </si>
-  <si>
-    <t>0.9763,0.0001,0.0005,0.0149</t>
-  </si>
-  <si>
-    <t>0.3908,0.0003,0.0010,0.8495</t>
-  </si>
-  <si>
-    <t>0.7812,0.0010,0.0067,0.2389</t>
-  </si>
-  <si>
-    <t>0.9298,0.0001,0.0006,0.0870</t>
-  </si>
-  <si>
-    <t>0.3116,0.5691,0.1386,0.0006</t>
-  </si>
-  <si>
-    <t>0.9831,0.0015,0.0018,0.0042</t>
-  </si>
-  <si>
-    <t>0.9343,0.0235,0.0083,0.0040</t>
-  </si>
-  <si>
-    <t>0.9325,0.0077,0.0064,0.0298</t>
-  </si>
-  <si>
-    <t>0.8723,0.0354,0.0533,0.0144</t>
-  </si>
-  <si>
-    <t>0.9171,0.0202,0.0191,0.0122</t>
-  </si>
-  <si>
-    <t>0.9653,0.0009,0.0011,0.0189</t>
-  </si>
-  <si>
-    <t>0.9361,0.0033,0.0080,0.0274</t>
-  </si>
-  <si>
-    <t>0.3866,0.1148,0.6588,0.0558</t>
-  </si>
-  <si>
-    <t>0.6677,0.0008,0.0060,0.3535</t>
-  </si>
-  <si>
-    <t>0.9856,0.0005,0.0006,0.0051</t>
-  </si>
-  <si>
-    <t>0.9197,0.0171,0.0089,0.0079</t>
-  </si>
-  <si>
-    <t>0.9873,0.0003,0.0030,0.0013</t>
-  </si>
-  <si>
-    <t>0.9402,0.0135,0.0200,0.0042</t>
-  </si>
-  <si>
-    <t>0.8243,0.0257,0.1601,0.0080</t>
-  </si>
-  <si>
-    <t>0.9698,0.0029,0.0152,0.0011</t>
-  </si>
-  <si>
-    <t>0.9875,0.0007,0.0019,0.0016</t>
-  </si>
-  <si>
-    <t>0.9224,0.0051,0.0038,0.0368</t>
-  </si>
-  <si>
-    <t>0.9174,0.0017,0.0022,0.1036</t>
-  </si>
-  <si>
-    <t>0.9046,0.0051,0.0103,0.0262</t>
-  </si>
-  <si>
-    <t>0.8943,0.0018,0.0047,0.0856</t>
-  </si>
-  <si>
-    <t>0.9442,0.0030,0.0020,0.0305</t>
-  </si>
-  <si>
-    <t>0.8754,0.0059,0.0072,0.0859</t>
-  </si>
-  <si>
-    <t>0.8332,0.0129,0.0056,0.0947</t>
-  </si>
-  <si>
-    <t>0.8674,0.0079,0.0044,0.0757</t>
-  </si>
-  <si>
-    <t>0.9746,0.0010,0.0031,0.0032</t>
-  </si>
-  <si>
-    <t>0.9574,0.0045,0.0119,0.0052</t>
-  </si>
-  <si>
-    <t>0.9729,0.0052,0.0076,0.0014</t>
-  </si>
-  <si>
-    <t>0.2293,0.2482,0.7050,0.0252</t>
-  </si>
-  <si>
-    <t>0.9834,0.0029,0.0012,0.0023</t>
-  </si>
-  <si>
-    <t>0.9282,0.0076,0.0166,0.0189</t>
-  </si>
-  <si>
-    <t>0.9656,0.0038,0.0052,0.0058</t>
-  </si>
-  <si>
-    <t>0.9274,0.0144,0.0116,0.0096</t>
-  </si>
-  <si>
-    <t>0.1088,0.4112,0.8601,0.0205</t>
-  </si>
-  <si>
-    <t>0.9367,0.0058,0.0039,0.0281</t>
-  </si>
-  <si>
-    <t>0.1857,0.0162,0.9236,0.0005</t>
-  </si>
-  <si>
-    <t>0.0773,0.0154,0.9755,0.0002</t>
-  </si>
-  <si>
-    <t>0.7780,0.0199,0.2811,0.0065</t>
-  </si>
-  <si>
-    <t>0.0291,0.0943,0.9708,0.0004</t>
-  </si>
-  <si>
-    <t>0.1481,0.0132,0.9352,0.0005</t>
-  </si>
-  <si>
-    <t>0.2479,0.0055,0.9055,0.0003</t>
-  </si>
-  <si>
-    <t>0.3344,0.0364,0.7542,0.0046</t>
-  </si>
-  <si>
-    <t>0.9618,0.0025,0.0374,0.0007</t>
-  </si>
-  <si>
-    <t>0.8990,0.0057,0.1194,0.0019</t>
-  </si>
-  <si>
-    <t>0.9746,0.0008,0.0188,0.0008</t>
-  </si>
-  <si>
-    <t>0.8788,0.0232,0.0914,0.0023</t>
-  </si>
-  <si>
-    <t>0.9369,0.0153,0.0252,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0003,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9604,0.0025,0.0260,0.0008</t>
-  </si>
-  <si>
-    <t>0.8882,0.0061,0.0997,0.0049</t>
-  </si>
-  <si>
-    <t>0.8665,0.1003,0.0112,0.0031</t>
-  </si>
-  <si>
-    <t>0.9459,0.0235,0.0040,0.0018</t>
-  </si>
-  <si>
-    <t>0.9204,0.0187,0.0171,0.0155</t>
-  </si>
-  <si>
-    <t>0.9277,0.0074,0.0051,0.0375</t>
-  </si>
-  <si>
-    <t>0.8953,0.0481,0.0079,0.0056</t>
-  </si>
-  <si>
-    <t>0.9562,0.0031,0.0309,0.0013</t>
-  </si>
-  <si>
-    <t>0.9558,0.0037,0.0263,0.0011</t>
-  </si>
-  <si>
-    <t>0.9564,0.0015,0.0205,0.0023</t>
-  </si>
-  <si>
-    <t>0.9764,0.0005,0.0144,0.0008</t>
-  </si>
-  <si>
-    <t>0.9808,0.0009,0.0124,0.0006</t>
-  </si>
-  <si>
-    <t>0.7385,0.0033,0.2736,0.0081</t>
-  </si>
-  <si>
-    <t>0.8094,0.0119,0.2066,0.0087</t>
-  </si>
-  <si>
-    <t>0.0841,0.0311,0.9609,0.0010</t>
-  </si>
-  <si>
-    <t>0.7838,0.0037,0.3604,0.0004</t>
-  </si>
-  <si>
-    <t>0.1337,0.1691,0.8463,0.0020</t>
-  </si>
-  <si>
-    <t>0.8536,0.0079,0.0032,0.0883</t>
-  </si>
-  <si>
-    <t>0.9442,0.0046,0.0022,0.0237</t>
-  </si>
-  <si>
-    <t>0.9356,0.0026,0.0018,0.0420</t>
-  </si>
-  <si>
-    <t>0.9737,0.0034,0.0034,0.0053</t>
-  </si>
-  <si>
-    <t>0.8343,0.0146,0.0048,0.0798</t>
-  </si>
-  <si>
-    <t>0.8927,0.0039,0.0057,0.0756</t>
-  </si>
-  <si>
-    <t>0.9734,0.0010,0.0003,0.0180</t>
-  </si>
-  <si>
-    <t>0.9816,0.0007,0.0006,0.0082</t>
-  </si>
-  <si>
-    <t>0.5834,0.0703,0.4616,0.0042</t>
-  </si>
-  <si>
-    <t>0.8796,0.0229,0.0420,0.0085</t>
-  </si>
-  <si>
-    <t>0.9059,0.0041,0.0191,0.0305</t>
-  </si>
-  <si>
-    <t>0.1266,0.0087,0.9167,0.0004</t>
-  </si>
-  <si>
-    <t>0.0082,0.0116,0.9873,0.0006</t>
-  </si>
-  <si>
-    <t>0.9576,0.0020,0.0413,0.0008</t>
-  </si>
-  <si>
-    <t>0.2509,0.0321,0.8586,0.0006</t>
-  </si>
-  <si>
-    <t>0.7742,0.0372,0.2679,0.0009</t>
-  </si>
-  <si>
-    <t>0.0097,0.0074,0.9871,0.0011</t>
-  </si>
-  <si>
-    <t>0.4388,0.0303,0.6189,0.0025</t>
-  </si>
-  <si>
-    <t>0.9419,0.0056,0.0456,0.0009</t>
-  </si>
-  <si>
-    <t>0.9917,0.0002,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.9762,0.0005,0.0176,0.0010</t>
-  </si>
-  <si>
-    <t>0.9815,0.0003,0.0144,0.0003</t>
-  </si>
-  <si>
-    <t>0.9127,0.0019,0.0025,0.0779</t>
-  </si>
-  <si>
-    <t>0.9182,0.0032,0.0022,0.0850</t>
-  </si>
-  <si>
-    <t>0.9140,0.0238,0.0082,0.0153</t>
-  </si>
-  <si>
-    <t>0.9569,0.0035,0.0022,0.0167</t>
-  </si>
-  <si>
-    <t>0.9543,0.0038,0.0020,0.0200</t>
-  </si>
-  <si>
-    <t>0.9412,0.0070,0.0072,0.0152</t>
-  </si>
-  <si>
-    <t>0.9669,0.0003,0.0003,0.0437</t>
-  </si>
-  <si>
-    <t>0.9287,0.0018,0.0006,0.0590</t>
-  </si>
-  <si>
-    <t>0.6525,0.1031,0.2572,0.0020</t>
-  </si>
-  <si>
-    <t>0.4284,0.0212,0.6987,0.0009</t>
-  </si>
-  <si>
-    <t>0.0311,0.0287,0.9851,0.0003</t>
-  </si>
-  <si>
-    <t>0.9089,0.0076,0.0992,0.0015</t>
-  </si>
-  <si>
-    <t>0.5567,0.0311,0.5778,0.0012</t>
-  </si>
-  <si>
-    <t>0.7721,0.0074,0.2063,0.0099</t>
-  </si>
-  <si>
-    <t>0.9841,0.0005,0.0091,0.0005</t>
-  </si>
-  <si>
-    <t>0.3360,0.0519,0.7051,0.0067</t>
-  </si>
-  <si>
-    <t>0.9589,0.0002,0.0022,0.0114</t>
-  </si>
-  <si>
-    <t>0.9777,0.0003,0.0017,0.0074</t>
-  </si>
-  <si>
-    <t>0.9223,0.0018,0.0020,0.0479</t>
-  </si>
-  <si>
-    <t>0.8327,0.0002,0.0022,0.1596</t>
-  </si>
-  <si>
-    <t>0.5525,0.0001,0.0011,0.6176</t>
-  </si>
-  <si>
-    <t>0.9316,0.0095,0.0198,0.0113</t>
+    <t>0.8344,0.0144,0.0700,0.0580</t>
+  </si>
+  <si>
+    <t>0.0509,0.0022,0.0017,0.9794</t>
+  </si>
+  <si>
+    <t>0.9173,0.0074,0.0043,0.0839</t>
+  </si>
+  <si>
+    <t>0.2206,0.0021,0.0006,0.9078</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0040,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9916,0.0035,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9959,0.0024,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9650,0.0016,0.0323,0.0010</t>
+  </si>
+  <si>
+    <t>0.0175,0.0111,0.9715,0.0148</t>
+  </si>
+  <si>
+    <t>0.0379,0.0133,0.9636,0.0004</t>
+  </si>
+  <si>
+    <t>0.0104,0.0074,0.9805,0.0010</t>
+  </si>
+  <si>
+    <t>0.6733,0.0055,0.3363,0.0162</t>
+  </si>
+  <si>
+    <t>0.0008,0.9970,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.9974,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0369,0.9706,0.0032,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.9921,0.0072,0.0028</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.9402,0.0036,0.0151,0.0142</t>
+  </si>
+  <si>
+    <t>0.5117,0.0604,0.4274,0.0230</t>
+  </si>
+  <si>
+    <t>0.0069,0.0068,0.9831,0.0031</t>
+  </si>
+  <si>
+    <t>0.3180,0.0036,0.7721,0.0028</t>
+  </si>
+  <si>
+    <t>0.0785,0.0035,0.9475,0.0034</t>
+  </si>
+  <si>
+    <t>0.0287,0.0053,0.9833,0.0012</t>
+  </si>
+  <si>
+    <t>0.0013,0.0022,0.9961,0.0021</t>
+  </si>
+  <si>
+    <t>0.0661,0.9033,0.0649,0.0090</t>
+  </si>
+  <si>
+    <t>0.8698,0.1362,0.0234,0.0027</t>
+  </si>
+  <si>
+    <t>0.0051,0.0337,0.9847,0.0048</t>
+  </si>
+  <si>
+    <t>0.0215,0.8973,0.0498,0.0006</t>
+  </si>
+  <si>
+    <t>0.9303,0.0393,0.0152,0.0085</t>
+  </si>
+  <si>
+    <t>0.8428,0.0739,0.1002,0.0269</t>
+  </si>
+  <si>
+    <t>0.5460,0.5686,0.0081,0.0021</t>
+  </si>
+  <si>
+    <t>0.0134,0.9773,0.0417,0.0037</t>
+  </si>
+  <si>
+    <t>0.0082,0.9066,0.0438,0.0181</t>
+  </si>
+  <si>
+    <t>0.0368,0.0076,0.9626,0.0027</t>
+  </si>
+  <si>
+    <t>0.1117,0.0865,0.8862,0.0025</t>
+  </si>
+  <si>
+    <t>0.0658,0.0023,0.8136,0.0583</t>
+  </si>
+  <si>
+    <t>0.0050,0.1545,0.9782,0.0010</t>
+  </si>
+  <si>
+    <t>0.0027,0.9950,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0032,0.9957,0.0005</t>
+  </si>
+  <si>
+    <t>0.0143,0.3271,0.0026,0.9155</t>
+  </si>
+  <si>
+    <t>0.0066,0.9750,0.0196,0.0178</t>
+  </si>
+  <si>
+    <t>0.0075,0.9894,0.0106,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.9954,0.0357,0.0005</t>
+  </si>
+  <si>
+    <t>0.0019,0.1348,0.9392,0.0039</t>
+  </si>
+  <si>
+    <t>0.0016,0.4229,0.9908,0.0012</t>
+  </si>
+  <si>
+    <t>0.0066,0.0470,0.9754,0.0142</t>
+  </si>
+  <si>
+    <t>0.0142,0.0007,0.9792,0.0035</t>
+  </si>
+  <si>
+    <t>0.0087,0.0068,0.9833,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.0032,0.9936,0.0008</t>
+  </si>
+  <si>
+    <t>0.9876,0.0039,0.0002,0.0047</t>
+  </si>
+  <si>
+    <t>0.9921,0.0036,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9956,0.0018,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.0012,0.0033,0.9940,0.0941</t>
+  </si>
+  <si>
+    <t>0.9809,0.0160,0.0034,0.0022</t>
+  </si>
+  <si>
+    <t>0.9846,0.0132,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.9855,0.0136,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.0007,0.9792,0.9626,0.0004</t>
+  </si>
+  <si>
+    <t>0.0188,0.0406,0.9712,0.0056</t>
+  </si>
+  <si>
+    <t>0.0058,0.0233,0.9850,0.0028</t>
+  </si>
+  <si>
+    <t>0.0001,0.9879,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0072,0.0068,0.9871,0.0017</t>
+  </si>
+  <si>
+    <t>0.0013,0.9975,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0182,0.9777,0.0025,0.0011</t>
+  </si>
+  <si>
+    <t>0.7387,0.0095,0.2749,0.0305</t>
+  </si>
+  <si>
+    <t>0.8571,0.0204,0.0980,0.0163</t>
+  </si>
+  <si>
+    <t>0.0102,0.0051,0.9884,0.0129</t>
+  </si>
+  <si>
+    <t>0.0000,0.9917,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9747,0.9044,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9471,0.9817,0.0003</t>
+  </si>
+  <si>
+    <t>0.0067,0.0003,0.0077,0.9930</t>
+  </si>
+  <si>
+    <t>0.0013,0.0016,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0115,0.0002,0.0001,0.9971</t>
+  </si>
+  <si>
+    <t>0.1013,0.0005,0.0004,0.9738</t>
+  </si>
+  <si>
+    <t>0.0039,0.0005,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.0032,0.0034,0.0027,0.9966</t>
+  </si>
+  <si>
+    <t>0.0002,0.9892,0.9854,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9586,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.9801,0.0849,0.0007</t>
+  </si>
+  <si>
+    <t>0.0018,0.1881,0.9861,0.0008</t>
+  </si>
+  <si>
+    <t>0.0009,0.9954,0.0507,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9269,0.9540,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9851,0.0094,0.0023,0.0028</t>
+  </si>
+  <si>
+    <t>0.9884,0.0140,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9897,0.0013,0.0003,0.0073</t>
+  </si>
+  <si>
+    <t>0.9944,0.0036,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9868,0.0054,0.0015,0.0044</t>
+  </si>
+  <si>
+    <t>0.9920,0.0074,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0011,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9967,0.0027,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.0375,0.0060,0.9714,0.0043</t>
+  </si>
+  <si>
+    <t>0.0451,0.0163,0.9621,0.0016</t>
+  </si>
+  <si>
+    <t>0.9226,0.0065,0.0658,0.0040</t>
+  </si>
+  <si>
+    <t>0.0063,0.0014,0.9876,0.0021</t>
+  </si>
+  <si>
+    <t>0.0081,0.9854,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.0057,0.9918,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.0267,0.9685,0.0054,0.0022</t>
+  </si>
+  <si>
+    <t>0.0056,0.9924,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0073,0.9804,0.0022,0.0050</t>
+  </si>
+  <si>
+    <t>0.0009,0.9956,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.9203,0.1290,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.7995,0.0123,0.1283,0.0508</t>
+  </si>
+  <si>
+    <t>0.1838,0.0060,0.8594,0.0081</t>
+  </si>
+  <si>
+    <t>0.3044,0.0647,0.6591,0.0590</t>
+  </si>
+  <si>
+    <t>0.8979,0.0128,0.0901,0.0067</t>
+  </si>
+  <si>
+    <t>0.0350,0.0590,0.0235,0.9473</t>
+  </si>
+  <si>
+    <t>0.0018,0.9944,0.0147,0.0010</t>
+  </si>
+  <si>
+    <t>0.0048,0.9883,0.0135,0.0035</t>
+  </si>
+  <si>
+    <t>0.0003,0.9974,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.0006,0.9940,0.3531,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.9965,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.5669,0.4972,0.0167,0.0049</t>
+  </si>
+  <si>
+    <t>0.4476,0.6692,0.0081,0.0031</t>
+  </si>
+  <si>
+    <t>0.9966,0.0009,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0015,0.0008,0.0029</t>
+  </si>
+  <si>
+    <t>0.9771,0.0046,0.0146,0.0032</t>
+  </si>
+  <si>
+    <t>0.9870,0.0128,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9949,0.0007,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9685,0.0102,0.0161,0.0051</t>
+  </si>
+  <si>
+    <t>0.9942,0.0006,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9940,0.0013,0.0008,0.0018</t>
+  </si>
+  <si>
+    <t>0.0006,0.7089,0.9959,0.0008</t>
+  </si>
+  <si>
+    <t>0.0008,0.9736,0.9400,0.0004</t>
+  </si>
+  <si>
+    <t>0.0105,0.0690,0.9557,0.0038</t>
+  </si>
+  <si>
+    <t>0.0395,0.6113,0.4505,0.0026</t>
+  </si>
+  <si>
+    <t>0.9851,0.0011,0.0111,0.0005</t>
+  </si>
+  <si>
+    <t>0.6497,0.0377,0.3706,0.0118</t>
+  </si>
+  <si>
+    <t>0.0154,0.0025,0.9853,0.0052</t>
+  </si>
+  <si>
+    <t>0.7137,0.0239,0.2047,0.0547</t>
+  </si>
+  <si>
+    <t>0.2247,0.0005,0.0001,0.9444</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0025,0.0043,0.0000,0.9987</t>
+  </si>
+  <si>
+    <t>0.0052,0.0001,0.0001,0.9989</t>
+  </si>
+  <si>
+    <t>0.0014,0.9309,0.9299,0.0009</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.0042,0.9851,0.0027,0.0119</t>
+  </si>
+  <si>
+    <t>0.9834,0.0012,0.0044,0.0053</t>
+  </si>
+  <si>
+    <t>0.2626,0.7580,0.0143,0.0113</t>
+  </si>
+  <si>
+    <t>0.9859,0.0019,0.0009,0.0100</t>
+  </si>
+  <si>
+    <t>0.4843,0.0021,0.0033,0.7365</t>
+  </si>
+  <si>
+    <t>0.9926,0.0017,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.0292,0.2093,0.9237,0.0744</t>
+  </si>
+  <si>
+    <t>0.6622,0.0026,0.0070,0.4333</t>
+  </si>
+  <si>
+    <t>0.9142,0.0046,0.0068,0.0879</t>
+  </si>
+  <si>
+    <t>0.1018,0.9003,0.0121,0.0068</t>
+  </si>
+  <si>
+    <t>0.9627,0.0151,0.0048,0.0078</t>
+  </si>
+  <si>
+    <t>0.9527,0.0269,0.0132,0.0046</t>
+  </si>
+  <si>
+    <t>0.5273,0.2952,0.1266,0.0524</t>
+  </si>
+  <si>
+    <t>0.9418,0.0480,0.0088,0.0020</t>
+  </si>
+  <si>
+    <t>0.9497,0.0499,0.0048,0.0020</t>
+  </si>
+  <si>
+    <t>0.9972,0.0017,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9937,0.0016,0.0012,0.0020</t>
+  </si>
+  <si>
+    <t>0.9934,0.0005,0.0001,0.0042</t>
+  </si>
+  <si>
+    <t>0.9945,0.0004,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.9926,0.0020,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.9670,0.0135,0.0125,0.0047</t>
+  </si>
+  <si>
+    <t>0.9901,0.0019,0.0012,0.0030</t>
+  </si>
+  <si>
+    <t>0.9927,0.0013,0.0020,0.0019</t>
+  </si>
+  <si>
+    <t>0.9811,0.0143,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.6305,0.4961,0.0103,0.0021</t>
+  </si>
+  <si>
+    <t>0.7674,0.2190,0.0107,0.0159</t>
+  </si>
+  <si>
+    <t>0.0061,0.1601,0.9884,0.0040</t>
+  </si>
+  <si>
+    <t>0.9948,0.0027,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9545,0.0344,0.0099,0.0035</t>
+  </si>
+  <si>
+    <t>0.9867,0.0067,0.0033,0.0013</t>
+  </si>
+  <si>
+    <t>0.9810,0.0072,0.0007,0.0045</t>
+  </si>
+  <si>
+    <t>0.0009,0.0215,0.9979,0.0007</t>
+  </si>
+  <si>
+    <t>0.9490,0.0382,0.0084,0.0056</t>
+  </si>
+  <si>
+    <t>0.0265,0.0050,0.9832,0.0006</t>
+  </si>
+  <si>
+    <t>0.0039,0.5018,0.9781,0.0033</t>
+  </si>
+  <si>
+    <t>0.1319,0.0067,0.9247,0.0072</t>
+  </si>
+  <si>
+    <t>0.0004,0.0137,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.0050,0.9946,0.0011</t>
+  </si>
+  <si>
+    <t>0.0092,0.0040,0.9906,0.0012</t>
+  </si>
+  <si>
+    <t>0.0032,0.0080,0.9885,0.0034</t>
+  </si>
+  <si>
+    <t>0.0237,0.0048,0.9587,0.0085</t>
+  </si>
+  <si>
+    <t>0.0319,0.0020,0.9681,0.0021</t>
+  </si>
+  <si>
+    <t>0.7292,0.0155,0.3462,0.0092</t>
+  </si>
+  <si>
+    <t>0.0837,0.6061,0.5447,0.0244</t>
+  </si>
+  <si>
+    <t>0.3399,0.1580,0.6134,0.0090</t>
+  </si>
+  <si>
+    <t>0.4751,0.2021,0.4117,0.0297</t>
+  </si>
+  <si>
+    <t>0.4545,0.0074,0.6923,0.0076</t>
+  </si>
+  <si>
+    <t>0.3631,0.0217,0.6451,0.0265</t>
+  </si>
+  <si>
+    <t>0.1548,0.8960,0.0062,0.0011</t>
+  </si>
+  <si>
+    <t>0.9806,0.0345,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9851,0.0211,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9893,0.0119,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9521,0.0709,0.0016,0.0030</t>
+  </si>
+  <si>
+    <t>0.7518,0.0488,0.2138,0.0079</t>
+  </si>
+  <si>
+    <t>0.9405,0.0016,0.0268,0.0092</t>
+  </si>
+  <si>
+    <t>0.8567,0.0073,0.0826,0.0288</t>
+  </si>
+  <si>
+    <t>0.7446,0.0132,0.3585,0.0079</t>
+  </si>
+  <si>
+    <t>0.6585,0.0029,0.2028,0.0437</t>
+  </si>
+  <si>
+    <t>0.0085,0.0088,0.9816,0.0221</t>
+  </si>
+  <si>
+    <t>0.0080,0.8441,0.8717,0.0061</t>
+  </si>
+  <si>
+    <t>0.0040,0.4423,0.9813,0.0017</t>
+  </si>
+  <si>
+    <t>0.0557,0.0776,0.9106,0.0036</t>
+  </si>
+  <si>
+    <t>0.0061,0.0231,0.9720,0.0052</t>
+  </si>
+  <si>
+    <t>0.9964,0.0004,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9949,0.0006,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9980,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9895,0.0032,0.0013,0.0027</t>
+  </si>
+  <si>
+    <t>0.9962,0.0015,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9815,0.0227,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9958,0.0002,0.0001,0.0032</t>
+  </si>
+  <si>
+    <t>0.0098,0.2555,0.9700,0.0117</t>
+  </si>
+  <si>
+    <t>0.0615,0.8096,0.1901,0.0237</t>
+  </si>
+  <si>
+    <t>0.3348,0.0112,0.7208,0.0285</t>
+  </si>
+  <si>
+    <t>0.0216,0.0146,0.9700,0.0040</t>
+  </si>
+  <si>
+    <t>0.0013,0.0017,0.9954,0.0025</t>
+  </si>
+  <si>
+    <t>0.0995,0.0518,0.8729,0.0042</t>
+  </si>
+  <si>
+    <t>0.0042,0.0037,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.0320,0.0088,0.9577,0.0024</t>
+  </si>
+  <si>
+    <t>0.0028,0.0197,0.9943,0.0009</t>
+  </si>
+  <si>
+    <t>0.0050,0.0045,0.9845,0.0061</t>
+  </si>
+  <si>
+    <t>0.0084,0.0345,0.9723,0.0040</t>
+  </si>
+  <si>
+    <t>0.8762,0.0063,0.1645,0.0055</t>
+  </si>
+  <si>
+    <t>0.8749,0.0080,0.1812,0.0064</t>
+  </si>
+  <si>
+    <t>0.9560,0.0002,0.0615,0.0004</t>
+  </si>
+  <si>
+    <t>0.9877,0.0089,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9938,0.0021,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.9932,0.0022,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0020,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9958,0.0009,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.0741,0.0450,0.9072,0.0010</t>
+  </si>
+  <si>
+    <t>0.0022,0.1147,0.9905,0.0012</t>
+  </si>
+  <si>
+    <t>0.0066,0.0197,0.9823,0.0017</t>
+  </si>
+  <si>
+    <t>0.0188,0.0364,0.9056,0.0038</t>
+  </si>
+  <si>
+    <t>0.0046,0.0084,0.9914,0.0003</t>
+  </si>
+  <si>
+    <t>0.0032,0.0040,0.9586,0.1753</t>
+  </si>
+  <si>
+    <t>0.2497,0.0044,0.8127,0.0064</t>
+  </si>
+  <si>
+    <t>0.0177,0.0026,0.9320,0.0389</t>
+  </si>
+  <si>
+    <t>0.1342,0.0114,0.0019,0.9306</t>
+  </si>
+  <si>
+    <t>0.0025,0.1759,0.0010,0.9919</t>
+  </si>
+  <si>
+    <t>0.1212,0.0009,0.0003,0.9652</t>
+  </si>
+  <si>
+    <t>0.0075,0.0001,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.8846,0.0030,0.0024,0.1155</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D223" t="s">
         <v>485</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
